--- a/public/import_template.xlsx
+++ b/public/import_template.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linnrnd/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linnrnd/Desktop/Bo_Bo_Yan_Zaw/laravel_projects/guest_table_planer/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CAEE7FF-06AB-1446-B0D3-CA3C598FAC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{404D2AE2-EEDC-7A4E-9D5B-EFB639F56397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2780" yWindow="1500" windowWidth="28040" windowHeight="17440" xr2:uid="{7EDE2F86-C432-5549-94A1-B91ECC4C5462}"/>
+    <workbookView xWindow="3180" yWindow="2000" windowWidth="27640" windowHeight="16940" xr2:uid="{3042F039-915E-EB49-83C6-6C37C23A9190}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,128 +36,31 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="4">
   <si>
-    <t>Date</t>
+    <t>No</t>
   </si>
   <si>
-    <t>Customer Name</t>
+    <t>Table</t>
   </si>
   <si>
-    <t>Phone Number</t>
+    <t>Name</t>
   </si>
   <si>
-    <t>Sale Person</t>
-  </si>
-  <si>
-    <t>Item Code</t>
-  </si>
-  <si>
-    <t>Item Name</t>
-  </si>
-  <si>
-    <t>Qty</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>Total Amount</t>
-  </si>
-  <si>
-    <t>Delivery Fees</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Sub-Category</t>
-  </si>
-  <si>
-    <t>Brand</t>
-  </si>
-  <si>
-    <t>Payment</t>
-  </si>
-  <si>
-    <t>State/Division</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>Station</t>
-  </si>
-  <si>
-    <t>Branch</t>
-  </si>
-  <si>
-    <t>Remark</t>
-  </si>
-  <si>
-    <t>Ther Su</t>
-  </si>
-  <si>
-    <t>Ei Hsu Han</t>
-  </si>
-  <si>
-    <t>TCL 50V6B 50-inch UHD 4K Google TV</t>
-  </si>
-  <si>
-    <t>Electronic</t>
-  </si>
-  <si>
-    <t>TV</t>
-  </si>
-  <si>
-    <t>TCL</t>
-  </si>
-  <si>
-    <t>Buy at Linn</t>
-  </si>
-  <si>
-    <t>NayPyiTaw</t>
-  </si>
-  <si>
-    <t>ပျဉ်းမနား</t>
-  </si>
-  <si>
-    <t>ဆိုင်လာယူ</t>
-  </si>
-  <si>
-    <t>Shop3(HO)</t>
-  </si>
-  <si>
-    <t>ပေါင်းလောင်းဆိုင်သို့လာယူပါသည်။</t>
+    <t>Guest 1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -180,13 +83,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,134 +418,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50C9E067-D798-CC4B-AF71-04EB7E511C13}">
-  <dimension ref="A1:U2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7F5772F-CAFB-5345-89CA-5EA69612040A}">
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="10.83203125" style="5"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
-        <v>45658</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="2">
-        <v>9962636502</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="2">
-        <v>51001300035</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="2">
-        <v>1</v>
-      </c>
-      <c r="H2" s="3">
-        <v>1355000</v>
-      </c>
-      <c r="I2" s="3">
-        <v>1355000</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
